--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,6 +924,702 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121592200</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>594409</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7186244</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121592195</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>594322</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7186145</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121592196</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>594308</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7186188</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121592198</v>
+      </c>
+      <c r="B7" t="n">
+        <v>82393</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>594333</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7186293</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121592199</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>594410</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7186244</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121592197</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56571</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>594312</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7186323</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592200</v>
+        <v>121592198</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594409</v>
+        <v>594333</v>
       </c>
       <c r="R4" t="n">
-        <v>7186244</v>
+        <v>7186293</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592195</v>
+        <v>121592200</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,39 +1055,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594322</v>
+        <v>594409</v>
       </c>
       <c r="R5" t="n">
-        <v>7186145</v>
+        <v>7186244</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1273,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592198</v>
+        <v>121592199</v>
       </c>
       <c r="B7" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,34 +1284,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594333</v>
+        <v>594410</v>
       </c>
       <c r="R7" t="n">
-        <v>7186293</v>
+        <v>7186244</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,7 +1385,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592199</v>
+        <v>121592195</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594410</v>
+        <v>594322</v>
       </c>
       <c r="R8" t="n">
-        <v>7186244</v>
+        <v>7186145</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592198</v>
+        <v>121592195</v>
       </c>
       <c r="B4" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,34 +943,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594333</v>
+        <v>594322</v>
       </c>
       <c r="R4" t="n">
-        <v>7186293</v>
+        <v>7186145</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1002,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1151,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592196</v>
+        <v>121592198</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,39 +1172,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594308</v>
+        <v>594333</v>
       </c>
       <c r="R6" t="n">
-        <v>7186188</v>
+        <v>7186293</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1385,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592195</v>
+        <v>121592197</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>56571</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,20 +1397,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1418,10 +1418,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1430,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594322</v>
+        <v>594312</v>
       </c>
       <c r="R8" t="n">
-        <v>7186145</v>
+        <v>7186323</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1465,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592197</v>
+        <v>121592196</v>
       </c>
       <c r="B9" t="n">
-        <v>56571</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,20 +1518,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1535,14 +1539,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594312</v>
+        <v>594308</v>
       </c>
       <c r="R9" t="n">
-        <v>7186323</v>
+        <v>7186188</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592200</v>
+        <v>121592197</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>56571</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,38 +1056,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594409</v>
+        <v>594312</v>
       </c>
       <c r="R5" t="n">
-        <v>7186244</v>
+        <v>7186323</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1138,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592198</v>
+        <v>121592196</v>
       </c>
       <c r="B6" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,34 +1181,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594333</v>
+        <v>594308</v>
       </c>
       <c r="R6" t="n">
-        <v>7186293</v>
+        <v>7186188</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1231,7 +1245,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1241,7 +1255,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1385,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592197</v>
+        <v>121592198</v>
       </c>
       <c r="B8" t="n">
-        <v>56571</v>
+        <v>82393</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,47 +1411,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102613</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594312</v>
+        <v>594333</v>
       </c>
       <c r="R8" t="n">
-        <v>7186323</v>
+        <v>7186293</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1469,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1484,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592196</v>
+        <v>121592200</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,39 +1527,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594308</v>
+        <v>594409</v>
       </c>
       <c r="R9" t="n">
-        <v>7186188</v>
+        <v>7186244</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592195</v>
+        <v>121592197</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>56571</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,20 +939,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -960,10 +960,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -972,10 +976,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594322</v>
+        <v>594312</v>
       </c>
       <c r="R4" t="n">
-        <v>7186145</v>
+        <v>7186323</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1007,7 +1011,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1021,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592197</v>
+        <v>121592195</v>
       </c>
       <c r="B5" t="n">
-        <v>56571</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,20 +1060,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1077,14 +1081,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594312</v>
+        <v>594322</v>
       </c>
       <c r="R5" t="n">
-        <v>7186323</v>
+        <v>7186145</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592196</v>
+        <v>121592200</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,39 +1181,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594308</v>
+        <v>594409</v>
       </c>
       <c r="R6" t="n">
-        <v>7186188</v>
+        <v>7186244</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1245,7 +1240,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1255,7 +1250,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1511,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592200</v>
+        <v>121592196</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,34 +1522,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594409</v>
+        <v>594308</v>
       </c>
       <c r="R9" t="n">
-        <v>7186244</v>
+        <v>7186188</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592200</v>
+        <v>121592199</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,31 +1181,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594409</v>
+        <v>594410</v>
       </c>
       <c r="R6" t="n">
         <v>7186244</v>
@@ -1277,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592199</v>
+        <v>121592200</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1293,36 +1298,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594410</v>
+        <v>594409</v>
       </c>
       <c r="R7" t="n">
         <v>7186244</v>

--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592199</v>
+        <v>121592200</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,36 +1181,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594410</v>
+        <v>594409</v>
       </c>
       <c r="R6" t="n">
         <v>7186244</v>
@@ -1282,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592200</v>
+        <v>121592199</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,31 +1293,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594409</v>
+        <v>594410</v>
       </c>
       <c r="R7" t="n">
         <v>7186244</v>

--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -927,7 +927,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592195</v>
+        <v>121592196</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -963,7 +963,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594322</v>
+        <v>594308</v>
       </c>
       <c r="R4" t="n">
-        <v>7186145</v>
+        <v>7186188</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592198</v>
+        <v>121592195</v>
       </c>
       <c r="B5" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,34 +1060,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594333</v>
+        <v>594322</v>
       </c>
       <c r="R5" t="n">
-        <v>7186293</v>
+        <v>7186145</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,7 +1124,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1134,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592197</v>
+        <v>121592200</v>
       </c>
       <c r="B6" t="n">
-        <v>56572</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,47 +1173,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594312</v>
+        <v>594409</v>
       </c>
       <c r="R6" t="n">
-        <v>7186323</v>
+        <v>7186244</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1240,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1250,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592199</v>
+        <v>121592198</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1293,39 +1289,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594410</v>
+        <v>594333</v>
       </c>
       <c r="R7" t="n">
-        <v>7186244</v>
+        <v>7186293</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1357,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,7 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592196</v>
+        <v>121592197</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>56572</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,20 +1397,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1427,10 +1418,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594308</v>
+        <v>594312</v>
       </c>
       <c r="R8" t="n">
-        <v>7186188</v>
+        <v>7186323</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1474,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592200</v>
+        <v>121592199</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,31 +1522,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594409</v>
+        <v>594410</v>
       </c>
       <c r="R9" t="n">
         <v>7186244</v>

--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592195</v>
+        <v>121592198</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,39 +1060,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594322</v>
+        <v>594333</v>
       </c>
       <c r="R5" t="n">
-        <v>7186145</v>
+        <v>7186293</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1124,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592200</v>
+        <v>121592197</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>56572</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,38 +1168,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594409</v>
+        <v>594312</v>
       </c>
       <c r="R6" t="n">
-        <v>7186244</v>
+        <v>7186323</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1236,7 +1240,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1250,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592198</v>
+        <v>121592199</v>
       </c>
       <c r="B7" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,34 +1293,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594333</v>
+        <v>594410</v>
       </c>
       <c r="R7" t="n">
-        <v>7186293</v>
+        <v>7186244</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1348,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1367,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592197</v>
+        <v>121592195</v>
       </c>
       <c r="B8" t="n">
-        <v>56572</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,20 +1406,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1418,14 +1427,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594312</v>
+        <v>594322</v>
       </c>
       <c r="R8" t="n">
-        <v>7186323</v>
+        <v>7186145</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1469,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1484,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592199</v>
+        <v>121592200</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,36 +1527,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594410</v>
+        <v>594409</v>
       </c>
       <c r="R9" t="n">
         <v>7186244</v>

--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -1394,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592195</v>
+        <v>121592200</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1410,39 +1410,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594322</v>
+        <v>594409</v>
       </c>
       <c r="R8" t="n">
-        <v>7186145</v>
+        <v>7186244</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1474,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592200</v>
+        <v>121592195</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,34 +1522,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594409</v>
+        <v>594322</v>
       </c>
       <c r="R9" t="n">
-        <v>7186244</v>
+        <v>7186145</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592197</v>
+        <v>121592199</v>
       </c>
       <c r="B6" t="n">
-        <v>56572</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,20 +1168,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1189,14 +1189,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1205,10 +1201,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594312</v>
+        <v>594410</v>
       </c>
       <c r="R6" t="n">
-        <v>7186323</v>
+        <v>7186244</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1240,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1250,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592199</v>
+        <v>121592197</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>56572</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,20 +1285,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1310,10 +1306,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594410</v>
+        <v>594312</v>
       </c>
       <c r="R7" t="n">
-        <v>7186244</v>
+        <v>7186323</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -927,7 +927,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592196</v>
+        <v>121592195</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -963,7 +963,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594308</v>
+        <v>594322</v>
       </c>
       <c r="R4" t="n">
-        <v>7186188</v>
+        <v>7186145</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592198</v>
+        <v>121592197</v>
       </c>
       <c r="B5" t="n">
-        <v>82400</v>
+        <v>56572</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,38 +1056,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594333</v>
+        <v>594312</v>
       </c>
       <c r="R5" t="n">
-        <v>7186293</v>
+        <v>7186323</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1138,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1273,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592197</v>
+        <v>121592200</v>
       </c>
       <c r="B7" t="n">
-        <v>56572</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,47 +1294,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594312</v>
+        <v>594409</v>
       </c>
       <c r="R7" t="n">
-        <v>7186323</v>
+        <v>7186244</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592200</v>
+        <v>121592198</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594409</v>
+        <v>594333</v>
       </c>
       <c r="R8" t="n">
-        <v>7186244</v>
+        <v>7186293</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,7 +1506,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592195</v>
+        <v>121592196</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1542,7 +1542,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594322</v>
+        <v>594308</v>
       </c>
       <c r="R9" t="n">
-        <v>7186145</v>
+        <v>7186188</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592195</v>
+        <v>121592197</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>56572</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,20 +939,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -960,10 +960,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -972,10 +976,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594322</v>
+        <v>594312</v>
       </c>
       <c r="R4" t="n">
-        <v>7186145</v>
+        <v>7186323</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1007,7 +1011,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1021,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592197</v>
+        <v>121592199</v>
       </c>
       <c r="B5" t="n">
-        <v>56572</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,20 +1060,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1077,14 +1081,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594312</v>
+        <v>594410</v>
       </c>
       <c r="R5" t="n">
-        <v>7186323</v>
+        <v>7186244</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592199</v>
+        <v>121592198</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,39 +1181,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594410</v>
+        <v>594333</v>
       </c>
       <c r="R6" t="n">
-        <v>7186244</v>
+        <v>7186293</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1245,7 +1240,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1255,7 +1250,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1394,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592198</v>
+        <v>121592195</v>
       </c>
       <c r="B8" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1410,34 +1405,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594333</v>
+        <v>594322</v>
       </c>
       <c r="R8" t="n">
-        <v>7186293</v>
+        <v>7186145</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592197</v>
+        <v>121592198</v>
       </c>
       <c r="B4" t="n">
-        <v>56572</v>
+        <v>82400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,47 +939,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594312</v>
+        <v>594333</v>
       </c>
       <c r="R4" t="n">
-        <v>7186323</v>
+        <v>7186293</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1021,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,7 +1039,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592199</v>
+        <v>121592195</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1093,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594410</v>
+        <v>594322</v>
       </c>
       <c r="R5" t="n">
-        <v>7186244</v>
+        <v>7186145</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1128,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1138,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592198</v>
+        <v>121592196</v>
       </c>
       <c r="B6" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,34 +1172,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594333</v>
+        <v>594308</v>
       </c>
       <c r="R6" t="n">
-        <v>7186293</v>
+        <v>7186188</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1240,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1250,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1389,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592195</v>
+        <v>121592197</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>56572</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,20 +1397,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1422,10 +1418,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594322</v>
+        <v>594312</v>
       </c>
       <c r="R8" t="n">
-        <v>7186145</v>
+        <v>7186323</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,7 +1506,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592196</v>
+        <v>121592199</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1542,7 +1542,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594308</v>
+        <v>594410</v>
       </c>
       <c r="R9" t="n">
-        <v>7186188</v>
+        <v>7186244</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592198</v>
+        <v>121592195</v>
       </c>
       <c r="B4" t="n">
-        <v>82400</v>
+        <v>57365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,34 +943,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594333</v>
+        <v>594322</v>
       </c>
       <c r="R4" t="n">
-        <v>7186293</v>
+        <v>7186145</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1002,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592195</v>
+        <v>121592197</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>56580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,20 +1056,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1072,10 +1077,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1084,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594322</v>
+        <v>594312</v>
       </c>
       <c r="R5" t="n">
-        <v>7186145</v>
+        <v>7186323</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1138,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592196</v>
+        <v>121592199</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1192,7 +1201,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1201,10 +1210,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594308</v>
+        <v>594410</v>
       </c>
       <c r="R6" t="n">
-        <v>7186188</v>
+        <v>7186244</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1236,7 +1245,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1255,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,7 +1285,7 @@
         <v>121592200</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1385,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592197</v>
+        <v>121592196</v>
       </c>
       <c r="B8" t="n">
-        <v>56572</v>
+        <v>57365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,20 +1406,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1418,14 +1427,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594312</v>
+        <v>594308</v>
       </c>
       <c r="R8" t="n">
-        <v>7186323</v>
+        <v>7186188</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1469,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1484,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592199</v>
+        <v>121592198</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>82414</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,39 +1527,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594410</v>
+        <v>594333</v>
       </c>
       <c r="R9" t="n">
-        <v>7186244</v>
+        <v>7186293</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 57099-2024 artfynd.xlsx
+++ b/artfynd/A 57099-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56145613</v>
+        <v>56145612</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594416.3831560373</v>
+        <v>594302</v>
       </c>
       <c r="R2" t="n">
-        <v>7186229.321556201</v>
+        <v>7186187</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2015-08-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-08-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56145612</v>
+        <v>56145613</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594301.9314752184</v>
+        <v>594416</v>
       </c>
       <c r="R3" t="n">
-        <v>7186186.900533183</v>
+        <v>7186229</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,19 +854,9 @@
           <t>2015-08-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-08-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592195</v>
+        <v>121592198</v>
       </c>
       <c r="B4" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,39 +908,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594322</v>
+        <v>594333</v>
       </c>
       <c r="R4" t="n">
-        <v>7186145</v>
+        <v>7186293</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1007,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,59 +1004,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592197</v>
+        <v>121592200</v>
       </c>
       <c r="B5" t="n">
-        <v>56580</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594312</v>
+        <v>594409</v>
       </c>
       <c r="R5" t="n">
-        <v>7186323</v>
+        <v>7186244</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1128,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1138,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,15 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592199</v>
+        <v>121592195</v>
       </c>
       <c r="B6" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594410</v>
+        <v>594322</v>
       </c>
       <c r="R6" t="n">
-        <v>7186244</v>
+        <v>7186145</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1245,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1255,7 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,15 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592200</v>
+        <v>121592196</v>
       </c>
       <c r="B7" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,34 +1234,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594409</v>
+        <v>594308</v>
       </c>
       <c r="R7" t="n">
-        <v>7186244</v>
+        <v>7186188</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1357,7 +1298,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,7 +1308,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,15 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592196</v>
+        <v>121592199</v>
       </c>
       <c r="B8" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1366,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1439,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594308</v>
+        <v>594410</v>
       </c>
       <c r="R8" t="n">
-        <v>7186188</v>
+        <v>7186244</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1474,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,50 +1447,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592198</v>
+        <v>121592197</v>
       </c>
       <c r="B9" t="n">
-        <v>82414</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594333</v>
+        <v>594312</v>
       </c>
       <c r="R9" t="n">
-        <v>7186293</v>
+        <v>7186323</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1586,7 +1526,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1536,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
